--- a/Dowling/dowling-vs-crk-100226.xlsx
+++ b/Dowling/dowling-vs-crk-100226.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R97ab9651747f41f1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R01455a6580ec4a58"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -79,9 +94,6 @@
     <t>MOTION DIR</t>
   </si>
   <si>
-    <t>COVERAGE</t>
-  </si>
-  <si>
     <t>SERIES</t>
   </si>
   <si>
@@ -118,6 +130,12 @@
     <t>E-Alley</t>
   </si>
   <si>
+    <t>G TUCK K</t>
+  </si>
+  <si>
+    <t>MIAMI</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
@@ -127,9 +145,15 @@
     <t>A</t>
   </si>
   <si>
+    <t>G TUCK DOT</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
+    <t>STR TEX</t>
+  </si>
+  <si>
     <t>TWINS OPEN</t>
   </si>
   <si>
@@ -151,12 +175,18 @@
     <t>Complete</t>
   </si>
   <si>
+    <t>K GUN</t>
+  </si>
+  <si>
     <t>BAL</t>
   </si>
   <si>
     <t>OPEN</t>
   </si>
   <si>
+    <t>G GUN</t>
+  </si>
+  <si>
     <t>TRIPS PRO</t>
   </si>
   <si>
@@ -172,30 +202,48 @@
     <t>C</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
     <t>TRIPS</t>
   </si>
   <si>
     <t>Penalty</t>
   </si>
   <si>
+    <t>DOT</t>
+  </si>
+  <si>
+    <t>TANGO</t>
+  </si>
+  <si>
     <t>Sack</t>
   </si>
   <si>
     <t>Incomplete</t>
   </si>
   <si>
+    <t>DUKE</t>
+  </si>
+  <si>
     <t>IOWA ROBBER</t>
   </si>
   <si>
     <t>TWINS Y OFF OPEN</t>
   </si>
   <si>
+    <t>G TUCK DOT UNDER</t>
+  </si>
+  <si>
     <t>Scramble</t>
   </si>
   <si>
     <t>TWINS PRO</t>
   </si>
   <si>
+    <t>G TUCK</t>
+  </si>
+  <si>
     <t>Y TRIPS CLOSED</t>
   </si>
   <si>
@@ -208,6 +256,9 @@
     <t>Fair Catch</t>
   </si>
   <si>
+    <t>Q</t>
+  </si>
+  <si>
     <t>EMPTY</t>
   </si>
   <si>
@@ -223,6 +274,9 @@
     <t>IOWA</t>
   </si>
   <si>
+    <t>WRAP</t>
+  </si>
+  <si>
     <t>ACE</t>
   </si>
   <si>
@@ -232,6 +286,9 @@
     <t>Fumble</t>
   </si>
   <si>
+    <t>DOT UNDER</t>
+  </si>
+  <si>
     <t>DEUCE</t>
   </si>
   <si>
@@ -253,14 +310,20 @@
     <t>Punt</t>
   </si>
   <si>
+    <t>FLEX</t>
+  </si>
+  <si>
     <t>Y OFF TRIPS PRO</t>
+  </si>
+  <si>
+    <t>GUN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y129"/>
+  <dimension ref="A1:AC129"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -338,6 +401,18 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -347,7 +422,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -359,13 +434,13 @@
         <v>-40</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -376,7 +451,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -388,39 +463,45 @@
         <v>-20</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J3">
         <v>5</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L3">
         <v>7</v>
       </c>
       <c r="M3" t="s">
-        <v>34</v>
-      </c>
-      <c r="R3" t="s">
-        <v>35</v>
-      </c>
-      <c r="S3" t="s">
-        <v>36</v>
-      </c>
-      <c r="U3" t="s">
-        <v>35</v>
-      </c>
-      <c r="W3">
-        <v>3</v>
-      </c>
-      <c r="X3">
+        <v>38</v>
+      </c>
+      <c r="P3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3">
+        <v>3</v>
+      </c>
+      <c r="W3" t="s">
+        <v>41</v>
+      </c>
+      <c r="X3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB3">
         <v>1</v>
       </c>
     </row>
@@ -432,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -444,39 +525,45 @@
         <v>-25</v>
       </c>
       <c r="G4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" t="s">
         <v>35</v>
       </c>
-      <c r="H4" t="s">
-        <v>31</v>
-      </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J4">
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L4">
         <v>7</v>
       </c>
       <c r="M4" t="s">
-        <v>37</v>
-      </c>
-      <c r="R4" t="s">
-        <v>30</v>
-      </c>
-      <c r="S4" t="s">
-        <v>36</v>
-      </c>
-      <c r="U4" t="s">
-        <v>35</v>
-      </c>
-      <c r="W4">
-        <v>3</v>
-      </c>
-      <c r="X4">
+        <v>43</v>
+      </c>
+      <c r="P4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>40</v>
+      </c>
+      <c r="S4">
+        <v>3</v>
+      </c>
+      <c r="W4" t="s">
+        <v>34</v>
+      </c>
+      <c r="X4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB4">
         <v>1</v>
       </c>
     </row>
@@ -488,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -500,39 +587,45 @@
         <v>-28</v>
       </c>
       <c r="G5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" t="s">
         <v>35</v>
       </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J5">
         <v>-2</v>
       </c>
       <c r="K5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L5">
         <v>6</v>
       </c>
       <c r="M5" t="s">
-        <v>37</v>
-      </c>
-      <c r="R5" t="s">
-        <v>30</v>
-      </c>
-      <c r="S5" t="s">
-        <v>39</v>
-      </c>
-      <c r="U5" t="s">
-        <v>30</v>
-      </c>
-      <c r="W5">
-        <v>3</v>
-      </c>
-      <c r="X5">
+        <v>43</v>
+      </c>
+      <c r="P5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>46</v>
+      </c>
+      <c r="S5">
+        <v>3</v>
+      </c>
+      <c r="W5" t="s">
+        <v>34</v>
+      </c>
+      <c r="X5" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB5">
         <v>1</v>
       </c>
     </row>
@@ -544,7 +637,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -556,15 +649,15 @@
         <v>-26</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
-      </c>
-      <c r="X6">
+        <v>49</v>
+      </c>
+      <c r="AB6">
         <v>1</v>
       </c>
     </row>
@@ -576,7 +669,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -588,33 +681,36 @@
         <v>-40</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J7">
         <v>12</v>
       </c>
       <c r="K7" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L7">
         <v>6</v>
       </c>
       <c r="M7" t="s">
-        <v>43</v>
-      </c>
-      <c r="R7" t="s">
-        <v>30</v>
-      </c>
-      <c r="U7" t="s">
-        <v>35</v>
-      </c>
-      <c r="X7">
+        <v>51</v>
+      </c>
+      <c r="P7" t="s">
+        <v>44</v>
+      </c>
+      <c r="W7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB7">
         <v>1</v>
       </c>
     </row>
@@ -626,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -638,19 +734,19 @@
         <v>48</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I8" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L8">
         <v>7</v>
@@ -661,13 +757,16 @@
       <c r="O8">
         <v>3</v>
       </c>
-      <c r="R8" t="s">
-        <v>30</v>
-      </c>
-      <c r="U8" t="s">
-        <v>35</v>
-      </c>
-      <c r="X8">
+      <c r="P8" t="s">
+        <v>54</v>
+      </c>
+      <c r="W8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
     </row>
@@ -679,7 +778,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -691,33 +790,36 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" t="s">
         <v>35</v>
       </c>
-      <c r="H9" t="s">
-        <v>31</v>
-      </c>
       <c r="I9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J9">
         <v>2</v>
       </c>
       <c r="K9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L9">
         <v>5</v>
       </c>
       <c r="M9" t="s">
-        <v>29</v>
-      </c>
-      <c r="R9" t="s">
-        <v>30</v>
-      </c>
-      <c r="U9" t="s">
-        <v>35</v>
-      </c>
-      <c r="X9">
+        <v>33</v>
+      </c>
+      <c r="P9" t="s">
+        <v>44</v>
+      </c>
+      <c r="W9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB9">
         <v>1</v>
       </c>
     </row>
@@ -729,7 +831,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -741,36 +843,36 @@
         <v>42</v>
       </c>
       <c r="G10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" t="s">
         <v>35</v>
       </c>
-      <c r="H10" t="s">
-        <v>31</v>
-      </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L10">
         <v>6</v>
       </c>
       <c r="M10" t="s">
-        <v>37</v>
-      </c>
-      <c r="R10" t="s">
-        <v>46</v>
-      </c>
-      <c r="S10" t="s">
-        <v>47</v>
-      </c>
-      <c r="U10" t="s">
-        <v>35</v>
-      </c>
-      <c r="X10">
+        <v>43</v>
+      </c>
+      <c r="W10" t="s">
+        <v>55</v>
+      </c>
+      <c r="X10" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB10">
         <v>1</v>
       </c>
     </row>
@@ -782,7 +884,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D11">
         <v>4</v>
@@ -794,36 +896,39 @@
         <v>41</v>
       </c>
       <c r="G11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I11" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J11">
         <v>4</v>
       </c>
       <c r="K11" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L11">
         <v>8</v>
       </c>
       <c r="M11" t="s">
-        <v>37</v>
-      </c>
-      <c r="R11" t="s">
-        <v>35</v>
-      </c>
-      <c r="S11" t="s">
-        <v>48</v>
-      </c>
-      <c r="U11" t="s">
-        <v>35</v>
-      </c>
-      <c r="X11">
+        <v>43</v>
+      </c>
+      <c r="P11" t="s">
+        <v>57</v>
+      </c>
+      <c r="W11" t="s">
+        <v>41</v>
+      </c>
+      <c r="X11" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB11">
         <v>1</v>
       </c>
     </row>
@@ -835,7 +940,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -847,33 +952,36 @@
         <v>37</v>
       </c>
       <c r="G12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="J12">
         <v>37</v>
       </c>
       <c r="K12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L12">
         <v>6</v>
       </c>
       <c r="M12" t="s">
-        <v>37</v>
-      </c>
-      <c r="R12" t="s">
-        <v>30</v>
-      </c>
-      <c r="U12" t="s">
-        <v>35</v>
-      </c>
-      <c r="X12">
+        <v>43</v>
+      </c>
+      <c r="P12" t="s">
+        <v>44</v>
+      </c>
+      <c r="W12" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB12">
         <v>1</v>
       </c>
     </row>
@@ -885,7 +993,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -897,15 +1005,15 @@
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H13" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I13" t="s">
-        <v>51</v>
-      </c>
-      <c r="X13">
+        <v>61</v>
+      </c>
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
@@ -917,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -929,13 +1037,13 @@
         <v>-40</v>
       </c>
       <c r="G14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H14" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I14" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
@@ -946,7 +1054,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -958,39 +1066,45 @@
         <v>-20</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H15" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I15" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J15">
         <v>7</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L15">
         <v>5</v>
       </c>
       <c r="M15" t="s">
-        <v>52</v>
-      </c>
-      <c r="R15" t="s">
-        <v>35</v>
-      </c>
-      <c r="S15" t="s">
-        <v>53</v>
-      </c>
-      <c r="U15" t="s">
-        <v>30</v>
-      </c>
-      <c r="W15">
-        <v>6</v>
-      </c>
-      <c r="X15">
+        <v>62</v>
+      </c>
+      <c r="P15" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>40</v>
+      </c>
+      <c r="S15">
+        <v>6</v>
+      </c>
+      <c r="W15" t="s">
+        <v>41</v>
+      </c>
+      <c r="X15" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB15">
         <v>2</v>
       </c>
     </row>
@@ -1002,7 +1116,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -1014,27 +1128,33 @@
         <v>-27</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I16" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="J16">
         <v>-5</v>
       </c>
       <c r="K16" t="s">
-        <v>38</v>
-      </c>
-      <c r="R16" t="s">
-        <v>35</v>
-      </c>
-      <c r="S16" t="s">
-        <v>53</v>
-      </c>
-      <c r="W16">
-        <v>6</v>
-      </c>
-      <c r="X16">
+        <v>45</v>
+      </c>
+      <c r="P16" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>40</v>
+      </c>
+      <c r="S16">
+        <v>6</v>
+      </c>
+      <c r="W16" t="s">
+        <v>41</v>
+      </c>
+      <c r="X16" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB16">
         <v>2</v>
       </c>
     </row>
@@ -1046,7 +1166,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1058,19 +1178,19 @@
         <v>-22</v>
       </c>
       <c r="G17" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H17" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I17" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J17">
         <v>21</v>
       </c>
       <c r="K17" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L17">
         <v>6</v>
@@ -1081,19 +1201,22 @@
       <c r="O17">
         <v>5</v>
       </c>
-      <c r="R17" t="s">
-        <v>30</v>
-      </c>
-      <c r="S17" t="s">
-        <v>39</v>
-      </c>
-      <c r="U17" t="s">
-        <v>30</v>
-      </c>
-      <c r="W17">
-        <v>3</v>
-      </c>
-      <c r="X17">
+      <c r="Q17" t="s">
+        <v>40</v>
+      </c>
+      <c r="S17">
+        <v>3</v>
+      </c>
+      <c r="W17" t="s">
+        <v>34</v>
+      </c>
+      <c r="X17" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB17">
         <v>2</v>
       </c>
     </row>
@@ -1105,7 +1228,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1117,39 +1240,45 @@
         <v>-43</v>
       </c>
       <c r="G18" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H18" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I18" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J18">
         <v>3</v>
       </c>
       <c r="K18" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L18">
         <v>6</v>
       </c>
       <c r="M18" t="s">
-        <v>37</v>
-      </c>
-      <c r="R18" t="s">
-        <v>35</v>
-      </c>
-      <c r="S18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P18" t="s">
         <v>39</v>
       </c>
-      <c r="U18" t="s">
-        <v>35</v>
-      </c>
-      <c r="W18">
-        <v>3</v>
-      </c>
-      <c r="X18">
+      <c r="Q18" t="s">
+        <v>67</v>
+      </c>
+      <c r="S18">
+        <v>3</v>
+      </c>
+      <c r="W18" t="s">
+        <v>41</v>
+      </c>
+      <c r="X18" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB18">
         <v>2</v>
       </c>
     </row>
@@ -1161,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -1173,36 +1302,42 @@
         <v>-46</v>
       </c>
       <c r="G19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H19" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I19" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="J19">
         <v>-5</v>
       </c>
       <c r="K19" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L19">
         <v>6</v>
       </c>
-      <c r="R19" t="s">
-        <v>35</v>
-      </c>
-      <c r="S19" t="s">
+      <c r="P19" t="s">
         <v>39</v>
       </c>
-      <c r="U19" t="s">
-        <v>30</v>
-      </c>
-      <c r="W19">
-        <v>3</v>
-      </c>
-      <c r="X19">
+      <c r="Q19" t="s">
+        <v>67</v>
+      </c>
+      <c r="S19">
+        <v>3</v>
+      </c>
+      <c r="W19" t="s">
+        <v>41</v>
+      </c>
+      <c r="X19" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB19">
         <v>2</v>
       </c>
     </row>
@@ -1214,7 +1349,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D20">
         <v>3</v>
@@ -1226,19 +1361,19 @@
         <v>-41</v>
       </c>
       <c r="G20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H20" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I20" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -1249,19 +1384,25 @@
       <c r="O20">
         <v>4</v>
       </c>
-      <c r="R20" t="s">
-        <v>35</v>
+      <c r="P20" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>70</v>
       </c>
       <c r="S20" t="s">
-        <v>53</v>
-      </c>
-      <c r="U20" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="W20" t="s">
-        <v>57</v>
-      </c>
-      <c r="X20">
+        <v>41</v>
+      </c>
+      <c r="X20" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB20">
         <v>2</v>
       </c>
     </row>
@@ -1273,7 +1414,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -1285,15 +1426,15 @@
         <v>-41</v>
       </c>
       <c r="G21" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H21" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I21" t="s">
-        <v>41</v>
-      </c>
-      <c r="X21">
+        <v>49</v>
+      </c>
+      <c r="AB21">
         <v>2</v>
       </c>
     </row>
@@ -1305,7 +1446,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -1317,19 +1458,19 @@
         <v>50</v>
       </c>
       <c r="G22" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H22" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I22" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L22">
         <v>7</v>
@@ -1340,16 +1481,19 @@
       <c r="O22">
         <v>9</v>
       </c>
-      <c r="R22" t="s">
-        <v>30</v>
-      </c>
-      <c r="S22" t="s">
-        <v>58</v>
-      </c>
-      <c r="U22" t="s">
-        <v>35</v>
-      </c>
-      <c r="X22">
+      <c r="P22" t="s">
+        <v>66</v>
+      </c>
+      <c r="W22" t="s">
+        <v>34</v>
+      </c>
+      <c r="X22" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB22">
         <v>2</v>
       </c>
     </row>
@@ -1361,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -1373,36 +1517,39 @@
         <v>50</v>
       </c>
       <c r="G23" t="s">
+        <v>41</v>
+      </c>
+      <c r="H23" t="s">
         <v>35</v>
       </c>
-      <c r="H23" t="s">
-        <v>31</v>
-      </c>
       <c r="I23" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J23">
         <v>-6</v>
       </c>
       <c r="K23" t="s">
+        <v>37</v>
+      </c>
+      <c r="L23">
+        <v>6</v>
+      </c>
+      <c r="M23" t="s">
         <v>33</v>
       </c>
-      <c r="L23">
-        <v>6</v>
-      </c>
-      <c r="M23" t="s">
-        <v>29</v>
-      </c>
-      <c r="R23" t="s">
-        <v>30</v>
-      </c>
-      <c r="S23" t="s">
-        <v>36</v>
-      </c>
-      <c r="U23" t="s">
-        <v>30</v>
-      </c>
-      <c r="X23">
+      <c r="P23" t="s">
+        <v>73</v>
+      </c>
+      <c r="W23" t="s">
+        <v>34</v>
+      </c>
+      <c r="X23" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB23">
         <v>2</v>
       </c>
     </row>
@@ -1414,7 +1561,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -1426,33 +1573,36 @@
         <v>-44</v>
       </c>
       <c r="G24" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H24" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I24" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L24">
         <v>6</v>
       </c>
-      <c r="R24" t="s">
-        <v>35</v>
-      </c>
-      <c r="U24" t="s">
-        <v>30</v>
-      </c>
-      <c r="V24" t="s">
-        <v>35</v>
-      </c>
-      <c r="X24">
+      <c r="P24" t="s">
+        <v>66</v>
+      </c>
+      <c r="W24" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB24">
         <v>2</v>
       </c>
     </row>
@@ -1464,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -1476,30 +1626,33 @@
         <v>-45</v>
       </c>
       <c r="G25" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H25" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I25" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="J25">
         <v>12</v>
       </c>
       <c r="K25" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L25">
         <v>5</v>
       </c>
-      <c r="R25" t="s">
-        <v>35</v>
-      </c>
-      <c r="U25" t="s">
-        <v>30</v>
-      </c>
-      <c r="X25">
+      <c r="P25" t="s">
+        <v>66</v>
+      </c>
+      <c r="W25" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB25">
         <v>2</v>
       </c>
     </row>
@@ -1511,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1523,19 +1676,19 @@
         <v>43</v>
       </c>
       <c r="G26" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H26" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I26" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J26">
         <v>3</v>
       </c>
       <c r="K26" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L26">
         <v>7</v>
@@ -1546,16 +1699,19 @@
       <c r="O26">
         <v>1</v>
       </c>
-      <c r="R26" t="s">
-        <v>35</v>
-      </c>
-      <c r="S26" t="s">
-        <v>60</v>
-      </c>
-      <c r="U26" t="s">
-        <v>30</v>
-      </c>
-      <c r="X26">
+      <c r="P26" t="s">
+        <v>44</v>
+      </c>
+      <c r="W26" t="s">
+        <v>41</v>
+      </c>
+      <c r="X26" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB26">
         <v>2</v>
       </c>
     </row>
@@ -1567,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -1579,36 +1735,36 @@
         <v>40</v>
       </c>
       <c r="G27" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H27" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I27" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J27">
         <v>8</v>
       </c>
       <c r="K27" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L27">
         <v>6</v>
       </c>
       <c r="M27" t="s">
-        <v>29</v>
-      </c>
-      <c r="R27" t="s">
-        <v>46</v>
-      </c>
-      <c r="S27" t="s">
-        <v>47</v>
-      </c>
-      <c r="U27" t="s">
-        <v>30</v>
-      </c>
-      <c r="X27">
+        <v>33</v>
+      </c>
+      <c r="W27" t="s">
+        <v>55</v>
+      </c>
+      <c r="X27" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB27">
         <v>2</v>
       </c>
     </row>
@@ -1620,7 +1776,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -1632,19 +1788,19 @@
         <v>32</v>
       </c>
       <c r="G28" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H28" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I28" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J28">
         <v>16</v>
       </c>
       <c r="K28" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L28">
         <v>7</v>
@@ -1655,16 +1811,19 @@
       <c r="O28">
         <v>6</v>
       </c>
-      <c r="R28" t="s">
-        <v>35</v>
-      </c>
-      <c r="S28" t="s">
-        <v>60</v>
-      </c>
-      <c r="U28" t="s">
-        <v>35</v>
-      </c>
-      <c r="X28">
+      <c r="P28" t="s">
+        <v>44</v>
+      </c>
+      <c r="W28" t="s">
+        <v>41</v>
+      </c>
+      <c r="X28" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB28">
         <v>2</v>
       </c>
     </row>
@@ -1676,7 +1835,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1688,19 +1847,19 @@
         <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H29" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I29" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J29">
         <v>7</v>
       </c>
       <c r="K29" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L29">
         <v>7</v>
@@ -1711,16 +1870,19 @@
       <c r="O29">
         <v>3</v>
       </c>
-      <c r="R29" t="s">
-        <v>30</v>
-      </c>
-      <c r="S29" t="s">
-        <v>60</v>
-      </c>
-      <c r="U29" t="s">
-        <v>35</v>
-      </c>
-      <c r="X29">
+      <c r="P29" t="s">
+        <v>44</v>
+      </c>
+      <c r="W29" t="s">
+        <v>34</v>
+      </c>
+      <c r="X29" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB29">
         <v>2</v>
       </c>
     </row>
@@ -1732,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -1744,36 +1906,39 @@
         <v>9</v>
       </c>
       <c r="G30" t="s">
+        <v>41</v>
+      </c>
+      <c r="H30" t="s">
         <v>35</v>
       </c>
-      <c r="H30" t="s">
-        <v>31</v>
-      </c>
       <c r="I30" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J30">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L30">
         <v>7</v>
       </c>
       <c r="M30" t="s">
-        <v>29</v>
-      </c>
-      <c r="R30" t="s">
-        <v>30</v>
-      </c>
-      <c r="S30" t="s">
-        <v>61</v>
-      </c>
-      <c r="U30" t="s">
-        <v>30</v>
-      </c>
-      <c r="X30">
+        <v>33</v>
+      </c>
+      <c r="P30" t="s">
+        <v>76</v>
+      </c>
+      <c r="W30" t="s">
+        <v>34</v>
+      </c>
+      <c r="X30" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB30">
         <v>2</v>
       </c>
     </row>
@@ -1785,7 +1950,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D31">
         <v>3</v>
@@ -1794,7 +1959,7 @@
         <v>2</v>
       </c>
       <c r="G31" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -1808,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D32">
         <v>3</v>
@@ -1820,19 +1985,19 @@
         <v>8</v>
       </c>
       <c r="G32" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H32" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I32" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L32">
         <v>7</v>
@@ -1843,13 +2008,16 @@
       <c r="O32">
         <v>6</v>
       </c>
-      <c r="R32" t="s">
-        <v>35</v>
-      </c>
-      <c r="U32" t="s">
-        <v>35</v>
-      </c>
-      <c r="X32">
+      <c r="P32" t="s">
+        <v>44</v>
+      </c>
+      <c r="W32" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB32">
         <v>2</v>
       </c>
     </row>
@@ -1861,7 +2029,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -1873,36 +2041,39 @@
         <v>8</v>
       </c>
       <c r="G33" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H33" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I33" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="J33">
         <v>8</v>
       </c>
       <c r="K33" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L33">
         <v>8</v>
       </c>
       <c r="M33" t="s">
-        <v>37</v>
-      </c>
-      <c r="R33" t="s">
-        <v>35</v>
-      </c>
-      <c r="S33" t="s">
-        <v>60</v>
-      </c>
-      <c r="U33" t="s">
-        <v>30</v>
-      </c>
-      <c r="X33">
+        <v>43</v>
+      </c>
+      <c r="P33" t="s">
+        <v>44</v>
+      </c>
+      <c r="W33" t="s">
+        <v>41</v>
+      </c>
+      <c r="X33" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB33">
         <v>2</v>
       </c>
     </row>
@@ -1914,7 +2085,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1926,10 +2097,10 @@
         <v>3</v>
       </c>
       <c r="G34" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H34" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35">
@@ -1940,7 +2111,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1952,15 +2123,15 @@
         <v>3</v>
       </c>
       <c r="G35" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H35" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I35" t="s">
-        <v>51</v>
-      </c>
-      <c r="X35">
+        <v>61</v>
+      </c>
+      <c r="AB35">
         <v>2</v>
       </c>
     </row>
@@ -1972,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1984,13 +2155,13 @@
         <v>-40</v>
       </c>
       <c r="G36" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H36" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I36" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37">
@@ -2001,7 +2172,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2013,39 +2184,45 @@
         <v>-20</v>
       </c>
       <c r="G37" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H37" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I37" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37" t="s">
+        <v>45</v>
+      </c>
+      <c r="L37">
+        <v>6</v>
+      </c>
+      <c r="M37" t="s">
         <v>38</v>
       </c>
-      <c r="L37">
-        <v>6</v>
-      </c>
-      <c r="M37" t="s">
-        <v>34</v>
-      </c>
-      <c r="R37" t="s">
-        <v>30</v>
-      </c>
-      <c r="S37" t="s">
-        <v>63</v>
-      </c>
-      <c r="U37" t="s">
-        <v>30</v>
-      </c>
-      <c r="W37">
-        <v>3</v>
-      </c>
-      <c r="X37">
+      <c r="P37" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>40</v>
+      </c>
+      <c r="S37">
+        <v>3</v>
+      </c>
+      <c r="W37" t="s">
+        <v>34</v>
+      </c>
+      <c r="X37" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB37">
         <v>3</v>
       </c>
     </row>
@@ -2057,7 +2234,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -2069,19 +2246,19 @@
         <v>-20</v>
       </c>
       <c r="G38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H38" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I38" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J38">
         <v>17</v>
       </c>
       <c r="K38" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L38">
         <v>6</v>
@@ -2092,19 +2269,25 @@
       <c r="O38">
         <v>5</v>
       </c>
-      <c r="R38" t="s">
-        <v>35</v>
-      </c>
-      <c r="S38" t="s">
-        <v>53</v>
-      </c>
-      <c r="U38" t="s">
-        <v>35</v>
-      </c>
-      <c r="W38">
-        <v>6</v>
-      </c>
-      <c r="X38">
+      <c r="P38" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>67</v>
+      </c>
+      <c r="S38">
+        <v>6</v>
+      </c>
+      <c r="W38" t="s">
+        <v>41</v>
+      </c>
+      <c r="X38" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB38">
         <v>3</v>
       </c>
     </row>
@@ -2116,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2128,39 +2311,45 @@
         <v>-37</v>
       </c>
       <c r="G39" t="s">
+        <v>41</v>
+      </c>
+      <c r="H39" t="s">
         <v>35</v>
       </c>
-      <c r="H39" t="s">
-        <v>31</v>
-      </c>
       <c r="I39" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J39">
         <v>8</v>
       </c>
       <c r="K39" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L39">
         <v>5</v>
       </c>
       <c r="M39" t="s">
-        <v>34</v>
-      </c>
-      <c r="R39" t="s">
-        <v>30</v>
-      </c>
-      <c r="S39" t="s">
-        <v>53</v>
-      </c>
-      <c r="U39" t="s">
-        <v>35</v>
-      </c>
-      <c r="W39">
-        <v>3</v>
-      </c>
-      <c r="X39">
+        <v>38</v>
+      </c>
+      <c r="P39" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>40</v>
+      </c>
+      <c r="S39">
+        <v>3</v>
+      </c>
+      <c r="W39" t="s">
+        <v>34</v>
+      </c>
+      <c r="X39" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB39">
         <v>3</v>
       </c>
     </row>
@@ -2172,7 +2361,7 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -2184,19 +2373,19 @@
         <v>-45</v>
       </c>
       <c r="G40" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H40" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I40" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J40">
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L40">
         <v>6</v>
@@ -2207,19 +2396,22 @@
       <c r="O40">
         <v>5</v>
       </c>
-      <c r="R40" t="s">
-        <v>35</v>
-      </c>
-      <c r="S40" t="s">
-        <v>39</v>
-      </c>
-      <c r="U40" t="s">
-        <v>30</v>
-      </c>
-      <c r="W40">
-        <v>3</v>
-      </c>
-      <c r="X40">
+      <c r="Q40" t="s">
+        <v>40</v>
+      </c>
+      <c r="S40">
+        <v>3</v>
+      </c>
+      <c r="W40" t="s">
+        <v>41</v>
+      </c>
+      <c r="X40" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB40">
         <v>3</v>
       </c>
     </row>
@@ -2231,7 +2423,7 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D41">
         <v>3</v>
@@ -2243,39 +2435,45 @@
         <v>-45</v>
       </c>
       <c r="G41" t="s">
+        <v>41</v>
+      </c>
+      <c r="H41" t="s">
         <v>35</v>
       </c>
-      <c r="H41" t="s">
-        <v>31</v>
-      </c>
       <c r="I41" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L41">
         <v>7</v>
       </c>
       <c r="M41" t="s">
-        <v>29</v>
-      </c>
-      <c r="R41" t="s">
-        <v>30</v>
-      </c>
-      <c r="S41" t="s">
-        <v>39</v>
-      </c>
-      <c r="U41" t="s">
-        <v>35</v>
-      </c>
-      <c r="W41">
-        <v>3</v>
-      </c>
-      <c r="X41">
+        <v>33</v>
+      </c>
+      <c r="P41" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>40</v>
+      </c>
+      <c r="S41">
+        <v>3</v>
+      </c>
+      <c r="W41" t="s">
+        <v>34</v>
+      </c>
+      <c r="X41" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB41">
         <v>3</v>
       </c>
     </row>
@@ -2287,7 +2485,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -2299,15 +2497,15 @@
         <v>-45</v>
       </c>
       <c r="G42" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H42" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I42" t="s">
-        <v>64</v>
-      </c>
-      <c r="X42">
+        <v>80</v>
+      </c>
+      <c r="AB42">
         <v>3</v>
       </c>
     </row>
@@ -2319,7 +2517,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2331,19 +2529,19 @@
         <v>-20</v>
       </c>
       <c r="G43" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H43" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I43" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J43">
         <v>35</v>
       </c>
       <c r="K43" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L43">
         <v>7</v>
@@ -2354,16 +2552,19 @@
       <c r="O43">
         <v>6</v>
       </c>
-      <c r="R43" t="s">
-        <v>35</v>
-      </c>
-      <c r="S43" t="s">
-        <v>60</v>
-      </c>
-      <c r="U43" t="s">
-        <v>35</v>
-      </c>
-      <c r="X43">
+      <c r="P43" t="s">
+        <v>44</v>
+      </c>
+      <c r="W43" t="s">
+        <v>41</v>
+      </c>
+      <c r="X43" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB43">
         <v>3</v>
       </c>
     </row>
@@ -2375,7 +2576,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2387,19 +2588,19 @@
         <v>45</v>
       </c>
       <c r="G44" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H44" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I44" t="s">
+        <v>53</v>
+      </c>
+      <c r="J44">
+        <v>6</v>
+      </c>
+      <c r="K44" t="s">
         <v>45</v>
-      </c>
-      <c r="J44">
-        <v>6</v>
-      </c>
-      <c r="K44" t="s">
-        <v>38</v>
       </c>
       <c r="L44">
         <v>6</v>
@@ -2410,16 +2611,19 @@
       <c r="O44">
         <v>1</v>
       </c>
-      <c r="R44" t="s">
-        <v>30</v>
-      </c>
-      <c r="S44" t="s">
-        <v>65</v>
-      </c>
-      <c r="U44" t="s">
-        <v>30</v>
-      </c>
-      <c r="X44">
+      <c r="P44" t="s">
+        <v>81</v>
+      </c>
+      <c r="W44" t="s">
+        <v>34</v>
+      </c>
+      <c r="X44" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB44">
         <v>3</v>
       </c>
     </row>
@@ -2431,7 +2635,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -2443,36 +2647,39 @@
         <v>39</v>
       </c>
       <c r="G45" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H45" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I45" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J45">
         <v>5</v>
       </c>
       <c r="K45" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L45">
         <v>8</v>
       </c>
       <c r="M45" t="s">
-        <v>34</v>
-      </c>
-      <c r="R45" t="s">
-        <v>35</v>
-      </c>
-      <c r="S45" t="s">
-        <v>36</v>
-      </c>
-      <c r="U45" t="s">
-        <v>35</v>
-      </c>
-      <c r="X45">
+        <v>38</v>
+      </c>
+      <c r="P45" t="s">
+        <v>44</v>
+      </c>
+      <c r="W45" t="s">
+        <v>41</v>
+      </c>
+      <c r="X45" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB45">
         <v>3</v>
       </c>
     </row>
@@ -2484,7 +2691,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -2496,27 +2703,30 @@
         <v>34</v>
       </c>
       <c r="G46" t="s">
+        <v>41</v>
+      </c>
+      <c r="H46" t="s">
         <v>35</v>
       </c>
-      <c r="H46" t="s">
-        <v>31</v>
-      </c>
       <c r="I46" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="J46">
         <v>5</v>
       </c>
       <c r="K46" t="s">
-        <v>38</v>
-      </c>
-      <c r="R46" t="s">
-        <v>30</v>
-      </c>
-      <c r="U46" t="s">
-        <v>35</v>
-      </c>
-      <c r="X46">
+        <v>45</v>
+      </c>
+      <c r="P46" t="s">
+        <v>44</v>
+      </c>
+      <c r="W46" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB46">
         <v>3</v>
       </c>
     </row>
@@ -2528,7 +2738,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -2540,33 +2750,36 @@
         <v>29</v>
       </c>
       <c r="G47" t="s">
+        <v>41</v>
+      </c>
+      <c r="H47" t="s">
         <v>35</v>
       </c>
-      <c r="H47" t="s">
-        <v>31</v>
-      </c>
       <c r="I47" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J47">
         <v>5</v>
       </c>
       <c r="K47" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L47">
         <v>8</v>
       </c>
       <c r="M47" t="s">
-        <v>37</v>
-      </c>
-      <c r="R47" t="s">
-        <v>30</v>
-      </c>
-      <c r="U47" t="s">
-        <v>35</v>
-      </c>
-      <c r="X47">
+        <v>43</v>
+      </c>
+      <c r="P47" t="s">
+        <v>44</v>
+      </c>
+      <c r="W47" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB47">
         <v>3</v>
       </c>
     </row>
@@ -2578,7 +2791,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -2590,19 +2803,19 @@
         <v>24</v>
       </c>
       <c r="G48" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H48" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I48" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J48">
         <v>5</v>
       </c>
       <c r="K48" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L48">
         <v>7</v>
@@ -2613,16 +2826,19 @@
       <c r="O48">
         <v>3</v>
       </c>
-      <c r="R48" t="s">
-        <v>30</v>
-      </c>
-      <c r="S48" t="s">
-        <v>39</v>
-      </c>
-      <c r="U48" t="s">
-        <v>35</v>
-      </c>
-      <c r="X48">
+      <c r="P48" t="s">
+        <v>44</v>
+      </c>
+      <c r="W48" t="s">
+        <v>34</v>
+      </c>
+      <c r="X48" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB48">
         <v>3</v>
       </c>
     </row>
@@ -2634,7 +2850,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -2646,36 +2862,39 @@
         <v>19</v>
       </c>
       <c r="G49" t="s">
+        <v>41</v>
+      </c>
+      <c r="H49" t="s">
         <v>35</v>
       </c>
-      <c r="H49" t="s">
-        <v>31</v>
-      </c>
       <c r="I49" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J49">
         <v>-2</v>
       </c>
       <c r="K49" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L49">
         <v>8</v>
       </c>
       <c r="M49" t="s">
-        <v>29</v>
-      </c>
-      <c r="R49" t="s">
-        <v>30</v>
-      </c>
-      <c r="S49" t="s">
-        <v>61</v>
-      </c>
-      <c r="U49" t="s">
-        <v>30</v>
-      </c>
-      <c r="X49">
+        <v>33</v>
+      </c>
+      <c r="P49" t="s">
+        <v>76</v>
+      </c>
+      <c r="W49" t="s">
+        <v>34</v>
+      </c>
+      <c r="X49" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB49">
         <v>3</v>
       </c>
     </row>
@@ -2687,7 +2906,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D50">
         <v>3</v>
@@ -2699,33 +2918,36 @@
         <v>21</v>
       </c>
       <c r="G50" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H50" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I50" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="J50">
         <v>12</v>
       </c>
       <c r="K50" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L50">
         <v>7</v>
       </c>
-      <c r="R50" t="s">
-        <v>35</v>
-      </c>
-      <c r="S50" t="s">
-        <v>39</v>
-      </c>
-      <c r="U50" t="s">
-        <v>30</v>
-      </c>
-      <c r="X50">
+      <c r="P50" t="s">
+        <v>76</v>
+      </c>
+      <c r="W50" t="s">
+        <v>41</v>
+      </c>
+      <c r="X50" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB50">
         <v>3</v>
       </c>
     </row>
@@ -2737,7 +2959,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -2749,19 +2971,19 @@
         <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H51" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I51" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="J51">
         <v>9</v>
       </c>
       <c r="K51" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L51">
         <v>6</v>
@@ -2772,16 +2994,19 @@
       <c r="O51">
         <v>3</v>
       </c>
-      <c r="R51" t="s">
-        <v>35</v>
-      </c>
-      <c r="S51" t="s">
-        <v>65</v>
-      </c>
-      <c r="U51" t="s">
-        <v>35</v>
-      </c>
-      <c r="X51">
+      <c r="P51" t="s">
+        <v>81</v>
+      </c>
+      <c r="W51" t="s">
+        <v>41</v>
+      </c>
+      <c r="X51" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB51">
         <v>3</v>
       </c>
     </row>
@@ -2793,7 +3018,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2805,15 +3030,15 @@
         <v>3</v>
       </c>
       <c r="G52" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H52" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="I52" t="s">
-        <v>51</v>
-      </c>
-      <c r="X52">
+        <v>61</v>
+      </c>
+      <c r="AB52">
         <v>3</v>
       </c>
     </row>
@@ -2825,7 +3050,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -2837,13 +3062,13 @@
         <v>-40</v>
       </c>
       <c r="G53" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H53" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I53" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54">
@@ -2854,7 +3079,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2866,36 +3091,42 @@
         <v>-20</v>
       </c>
       <c r="G54" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H54" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I54" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J54">
         <v>3</v>
       </c>
       <c r="K54" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L54">
         <v>6</v>
       </c>
       <c r="M54" t="s">
-        <v>52</v>
-      </c>
-      <c r="R54" t="s">
-        <v>35</v>
-      </c>
-      <c r="S54" t="s">
-        <v>68</v>
-      </c>
-      <c r="U54" t="s">
-        <v>35</v>
-      </c>
-      <c r="X54">
+        <v>62</v>
+      </c>
+      <c r="P54" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>40</v>
+      </c>
+      <c r="W54" t="s">
+        <v>41</v>
+      </c>
+      <c r="X54" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB54">
         <v>4</v>
       </c>
     </row>
@@ -2907,7 +3138,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -2919,19 +3150,19 @@
         <v>-23</v>
       </c>
       <c r="G55" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H55" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I55" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J55">
         <v>15</v>
       </c>
       <c r="K55" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L55">
         <v>6</v>
@@ -2942,19 +3173,22 @@
       <c r="O55">
         <v>6</v>
       </c>
-      <c r="R55" t="s">
-        <v>30</v>
-      </c>
-      <c r="S55" t="s">
-        <v>39</v>
-      </c>
-      <c r="U55" t="s">
-        <v>35</v>
-      </c>
-      <c r="W55">
-        <v>3</v>
-      </c>
-      <c r="X55">
+      <c r="Q55" t="s">
+        <v>40</v>
+      </c>
+      <c r="S55">
+        <v>3</v>
+      </c>
+      <c r="W55" t="s">
+        <v>34</v>
+      </c>
+      <c r="X55" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB55">
         <v>4</v>
       </c>
     </row>
@@ -2966,7 +3200,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2978,19 +3212,19 @@
         <v>-38</v>
       </c>
       <c r="G56" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H56" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I56" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J56">
         <v>-4</v>
       </c>
       <c r="K56" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L56">
         <v>6</v>
@@ -3001,19 +3235,25 @@
       <c r="O56">
         <v>1</v>
       </c>
-      <c r="R56" t="s">
-        <v>30</v>
-      </c>
-      <c r="S56" t="s">
-        <v>53</v>
-      </c>
-      <c r="U56" t="s">
-        <v>30</v>
-      </c>
-      <c r="W56">
-        <v>6</v>
-      </c>
-      <c r="X56">
+      <c r="P56" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>40</v>
+      </c>
+      <c r="S56">
+        <v>6</v>
+      </c>
+      <c r="W56" t="s">
+        <v>34</v>
+      </c>
+      <c r="X56" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB56">
         <v>4</v>
       </c>
     </row>
@@ -3025,7 +3265,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -3037,19 +3277,19 @@
         <v>-34</v>
       </c>
       <c r="G57" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H57" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I57" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L57">
         <v>6</v>
@@ -3060,19 +3300,28 @@
       <c r="O57">
         <v>4</v>
       </c>
-      <c r="R57" t="s">
-        <v>35</v>
+      <c r="P57" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>40</v>
       </c>
       <c r="S57" t="s">
-        <v>53</v>
-      </c>
-      <c r="U57" t="s">
-        <v>30</v>
+        <v>86</v>
+      </c>
+      <c r="T57" t="s">
+        <v>87</v>
       </c>
       <c r="W57" t="s">
-        <v>69</v>
-      </c>
-      <c r="X57">
+        <v>41</v>
+      </c>
+      <c r="X57" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB57">
         <v>4</v>
       </c>
     </row>
@@ -3084,7 +3333,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D58">
         <v>3</v>
@@ -3096,19 +3345,19 @@
         <v>-34</v>
       </c>
       <c r="G58" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H58" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I58" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="J58">
         <v>10</v>
       </c>
       <c r="K58" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L58">
         <v>6</v>
@@ -3119,19 +3368,25 @@
       <c r="O58">
         <v>3</v>
       </c>
-      <c r="R58" t="s">
-        <v>46</v>
-      </c>
-      <c r="S58" t="s">
+      <c r="P58" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q58" t="s">
         <v>70</v>
       </c>
-      <c r="U58" t="s">
-        <v>35</v>
-      </c>
-      <c r="W58">
-        <v>6</v>
-      </c>
-      <c r="X58">
+      <c r="S58">
+        <v>6</v>
+      </c>
+      <c r="W58" t="s">
+        <v>55</v>
+      </c>
+      <c r="X58" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB58">
         <v>4</v>
       </c>
     </row>
@@ -3143,7 +3398,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D59">
         <v>3</v>
@@ -3155,19 +3410,19 @@
         <v>-44</v>
       </c>
       <c r="G59" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H59" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I59" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L59">
         <v>7</v>
@@ -3178,19 +3433,25 @@
       <c r="O59">
         <v>3</v>
       </c>
-      <c r="R59" t="s">
-        <v>35</v>
-      </c>
-      <c r="S59" t="s">
-        <v>39</v>
-      </c>
-      <c r="U59" t="s">
-        <v>35</v>
-      </c>
-      <c r="W59">
-        <v>6</v>
-      </c>
-      <c r="X59">
+      <c r="P59" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>67</v>
+      </c>
+      <c r="S59">
+        <v>6</v>
+      </c>
+      <c r="W59" t="s">
+        <v>41</v>
+      </c>
+      <c r="X59" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB59">
         <v>4</v>
       </c>
     </row>
@@ -3202,7 +3463,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3214,19 +3475,19 @@
         <v>42</v>
       </c>
       <c r="G60" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H60" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I60" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="J60">
         <v>15</v>
       </c>
       <c r="K60" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L60">
         <v>7</v>
@@ -3237,16 +3498,19 @@
       <c r="O60">
         <v>7</v>
       </c>
-      <c r="R60" t="s">
-        <v>35</v>
-      </c>
-      <c r="S60" t="s">
-        <v>39</v>
-      </c>
-      <c r="U60" t="s">
-        <v>30</v>
-      </c>
-      <c r="X60">
+      <c r="P60" t="s">
+        <v>44</v>
+      </c>
+      <c r="W60" t="s">
+        <v>41</v>
+      </c>
+      <c r="X60" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB60">
         <v>4</v>
       </c>
     </row>
@@ -3258,7 +3522,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3270,36 +3534,39 @@
         <v>27</v>
       </c>
       <c r="G61" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H61" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I61" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J61">
         <v>12</v>
       </c>
       <c r="K61" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L61">
         <v>8</v>
       </c>
       <c r="M61" t="s">
-        <v>37</v>
-      </c>
-      <c r="R61" t="s">
-        <v>35</v>
-      </c>
-      <c r="S61" t="s">
-        <v>60</v>
-      </c>
-      <c r="U61" t="s">
-        <v>30</v>
-      </c>
-      <c r="X61">
+        <v>43</v>
+      </c>
+      <c r="P61" t="s">
+        <v>44</v>
+      </c>
+      <c r="W61" t="s">
+        <v>41</v>
+      </c>
+      <c r="X61" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB61">
         <v>4</v>
       </c>
     </row>
@@ -3311,7 +3578,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3323,36 +3590,36 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H62" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I62" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J62">
         <v>13</v>
       </c>
       <c r="K62" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L62">
         <v>7</v>
       </c>
       <c r="M62" t="s">
-        <v>52</v>
-      </c>
-      <c r="R62" t="s">
-        <v>46</v>
-      </c>
-      <c r="S62" t="s">
-        <v>47</v>
-      </c>
-      <c r="U62" t="s">
-        <v>35</v>
-      </c>
-      <c r="X62">
+        <v>62</v>
+      </c>
+      <c r="W62" t="s">
+        <v>55</v>
+      </c>
+      <c r="X62" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB62">
         <v>4</v>
       </c>
     </row>
@@ -3364,7 +3631,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3376,36 +3643,39 @@
         <v>2</v>
       </c>
       <c r="G63" t="s">
+        <v>41</v>
+      </c>
+      <c r="H63" t="s">
         <v>35</v>
       </c>
-      <c r="H63" t="s">
-        <v>31</v>
-      </c>
       <c r="I63" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="J63">
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L63">
         <v>9</v>
       </c>
       <c r="M63" t="s">
-        <v>37</v>
-      </c>
-      <c r="R63" t="s">
-        <v>46</v>
-      </c>
-      <c r="S63" t="s">
-        <v>73</v>
-      </c>
-      <c r="U63" t="s">
-        <v>35</v>
-      </c>
-      <c r="X63">
+        <v>43</v>
+      </c>
+      <c r="P63" t="s">
+        <v>91</v>
+      </c>
+      <c r="W63" t="s">
+        <v>55</v>
+      </c>
+      <c r="X63" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB63">
         <v>4</v>
       </c>
     </row>
@@ -3417,7 +3687,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3429,39 +3699,45 @@
         <v>-4</v>
       </c>
       <c r="G64" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H64" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I64" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J64">
         <v>4</v>
       </c>
       <c r="K64" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L64">
         <v>6</v>
       </c>
       <c r="M64" t="s">
-        <v>43</v>
-      </c>
-      <c r="R64" t="s">
-        <v>35</v>
-      </c>
-      <c r="S64" t="s">
-        <v>39</v>
-      </c>
-      <c r="U64" t="s">
-        <v>30</v>
-      </c>
-      <c r="W64">
-        <v>3</v>
-      </c>
-      <c r="X64">
+        <v>51</v>
+      </c>
+      <c r="P64" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>40</v>
+      </c>
+      <c r="S64">
+        <v>3</v>
+      </c>
+      <c r="W64" t="s">
+        <v>41</v>
+      </c>
+      <c r="X64" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB64">
         <v>5</v>
       </c>
     </row>
@@ -3473,7 +3749,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -3485,19 +3761,19 @@
         <v>-8</v>
       </c>
       <c r="G65" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H65" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I65" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J65">
         <v>3</v>
       </c>
       <c r="K65" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L65">
         <v>5</v>
@@ -3508,19 +3784,25 @@
       <c r="O65">
         <v>3</v>
       </c>
-      <c r="R65" t="s">
-        <v>35</v>
-      </c>
-      <c r="S65" t="s">
-        <v>53</v>
-      </c>
-      <c r="U65" t="s">
-        <v>35</v>
-      </c>
-      <c r="W65">
-        <v>6</v>
-      </c>
-      <c r="X65">
+      <c r="P65" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>40</v>
+      </c>
+      <c r="S65">
+        <v>6</v>
+      </c>
+      <c r="W65" t="s">
+        <v>41</v>
+      </c>
+      <c r="X65" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB65">
         <v>5</v>
       </c>
     </row>
@@ -3532,7 +3814,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D66">
         <v>3</v>
@@ -3544,19 +3826,19 @@
         <v>-11</v>
       </c>
       <c r="G66" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H66" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I66" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J66">
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L66">
         <v>6</v>
@@ -3567,19 +3849,25 @@
       <c r="O66">
         <v>5</v>
       </c>
-      <c r="R66" t="s">
-        <v>35</v>
-      </c>
-      <c r="S66" t="s">
-        <v>53</v>
-      </c>
-      <c r="U66" t="s">
-        <v>35</v>
-      </c>
-      <c r="W66">
-        <v>3</v>
-      </c>
-      <c r="X66">
+      <c r="P66" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>40</v>
+      </c>
+      <c r="S66">
+        <v>3</v>
+      </c>
+      <c r="W66" t="s">
+        <v>41</v>
+      </c>
+      <c r="X66" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB66">
         <v>5</v>
       </c>
     </row>
@@ -3591,7 +3879,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D67">
         <v>4</v>
@@ -3603,15 +3891,15 @@
         <v>-11</v>
       </c>
       <c r="G67" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H67" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I67" t="s">
-        <v>41</v>
-      </c>
-      <c r="X67">
+        <v>49</v>
+      </c>
+      <c r="AB67">
         <v>5</v>
       </c>
     </row>
@@ -3623,7 +3911,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -3635,19 +3923,19 @@
         <v>35</v>
       </c>
       <c r="G68" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H68" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I68" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J68">
         <v>11</v>
       </c>
       <c r="K68" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L68">
         <v>7</v>
@@ -3658,13 +3946,16 @@
       <c r="O68">
         <v>1</v>
       </c>
-      <c r="R68" t="s">
-        <v>35</v>
-      </c>
-      <c r="U68" t="s">
-        <v>30</v>
-      </c>
-      <c r="X68">
+      <c r="P68" t="s">
+        <v>54</v>
+      </c>
+      <c r="W68" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB68">
         <v>5</v>
       </c>
     </row>
@@ -3676,7 +3967,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -3688,19 +3979,19 @@
         <v>24</v>
       </c>
       <c r="G69" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H69" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I69" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J69">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L69">
         <v>6</v>
@@ -3711,16 +4002,19 @@
       <c r="O69">
         <v>3</v>
       </c>
-      <c r="R69" t="s">
-        <v>35</v>
-      </c>
-      <c r="S69" t="s">
-        <v>65</v>
-      </c>
-      <c r="U69" t="s">
-        <v>35</v>
-      </c>
-      <c r="X69">
+      <c r="P69" t="s">
+        <v>81</v>
+      </c>
+      <c r="W69" t="s">
+        <v>41</v>
+      </c>
+      <c r="X69" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB69">
         <v>5</v>
       </c>
     </row>
@@ -3732,7 +4026,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -3744,33 +4038,36 @@
         <v>23</v>
       </c>
       <c r="G70" t="s">
+        <v>41</v>
+      </c>
+      <c r="H70" t="s">
         <v>35</v>
       </c>
-      <c r="H70" t="s">
-        <v>31</v>
-      </c>
       <c r="I70" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J70">
         <v>4</v>
       </c>
       <c r="K70" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L70">
         <v>7</v>
       </c>
       <c r="M70" t="s">
-        <v>37</v>
-      </c>
-      <c r="R70" t="s">
-        <v>35</v>
-      </c>
-      <c r="U70" t="s">
-        <v>35</v>
-      </c>
-      <c r="X70">
+        <v>43</v>
+      </c>
+      <c r="P70" t="s">
+        <v>66</v>
+      </c>
+      <c r="W70" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB70">
         <v>5</v>
       </c>
     </row>
@@ -3782,7 +4079,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D71">
         <v>3</v>
@@ -3794,36 +4091,39 @@
         <v>19</v>
       </c>
       <c r="G71" t="s">
+        <v>41</v>
+      </c>
+      <c r="H71" t="s">
         <v>35</v>
       </c>
-      <c r="H71" t="s">
-        <v>31</v>
-      </c>
       <c r="I71" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J71">
         <v>3</v>
       </c>
       <c r="K71" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L71">
         <v>8</v>
       </c>
       <c r="M71" t="s">
-        <v>43</v>
-      </c>
-      <c r="R71" t="s">
-        <v>30</v>
-      </c>
-      <c r="S71" t="s">
-        <v>48</v>
-      </c>
-      <c r="U71" t="s">
-        <v>35</v>
-      </c>
-      <c r="X71">
+        <v>51</v>
+      </c>
+      <c r="P71" t="s">
+        <v>29</v>
+      </c>
+      <c r="W71" t="s">
+        <v>34</v>
+      </c>
+      <c r="X71" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB71">
         <v>5</v>
       </c>
     </row>
@@ -3835,7 +4135,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D72">
         <v>4</v>
@@ -3847,36 +4147,36 @@
         <v>16</v>
       </c>
       <c r="G72" t="s">
+        <v>41</v>
+      </c>
+      <c r="H72" t="s">
         <v>35</v>
       </c>
-      <c r="H72" t="s">
-        <v>31</v>
-      </c>
       <c r="I72" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J72">
         <v>6</v>
       </c>
       <c r="K72" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L72">
         <v>8</v>
       </c>
       <c r="M72" t="s">
-        <v>43</v>
-      </c>
-      <c r="R72" t="s">
-        <v>30</v>
-      </c>
-      <c r="S72" t="s">
-        <v>60</v>
-      </c>
-      <c r="U72" t="s">
-        <v>35</v>
-      </c>
-      <c r="X72">
+        <v>51</v>
+      </c>
+      <c r="W72" t="s">
+        <v>34</v>
+      </c>
+      <c r="X72" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB72">
         <v>5</v>
       </c>
     </row>
@@ -3888,7 +4188,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -3900,19 +4200,19 @@
         <v>10</v>
       </c>
       <c r="G73" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H73" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I73" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J73">
         <v>5</v>
       </c>
       <c r="K73" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L73">
         <v>7</v>
@@ -3923,13 +4223,16 @@
       <c r="O73">
         <v>1</v>
       </c>
-      <c r="R73" t="s">
-        <v>35</v>
-      </c>
-      <c r="U73" t="s">
-        <v>30</v>
-      </c>
-      <c r="X73">
+      <c r="P73" t="s">
+        <v>54</v>
+      </c>
+      <c r="W73" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB73">
         <v>5</v>
       </c>
     </row>
@@ -3941,7 +4244,7 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D74">
         <v>2</v>
@@ -3953,33 +4256,33 @@
         <v>5</v>
       </c>
       <c r="G74" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H74" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I74" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J74">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L74">
         <v>6</v>
       </c>
-      <c r="R74" t="s">
-        <v>46</v>
-      </c>
-      <c r="S74" t="s">
-        <v>47</v>
-      </c>
-      <c r="U74" t="s">
-        <v>30</v>
-      </c>
-      <c r="X74">
+      <c r="W74" t="s">
+        <v>55</v>
+      </c>
+      <c r="X74" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB74">
         <v>5</v>
       </c>
     </row>
@@ -3991,7 +4294,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D75">
         <v>3</v>
@@ -4003,36 +4306,36 @@
         <v>4</v>
       </c>
       <c r="G75" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H75" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I75" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="J75">
         <v>4</v>
       </c>
       <c r="K75" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L75">
         <v>9</v>
       </c>
       <c r="M75" t="s">
-        <v>29</v>
-      </c>
-      <c r="R75" t="s">
-        <v>46</v>
-      </c>
-      <c r="S75" t="s">
-        <v>74</v>
-      </c>
-      <c r="U75" t="s">
-        <v>30</v>
-      </c>
-      <c r="X75">
+        <v>33</v>
+      </c>
+      <c r="W75" t="s">
+        <v>55</v>
+      </c>
+      <c r="X75" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB75">
         <v>5</v>
       </c>
     </row>
@@ -4044,7 +4347,7 @@
         <v>2</v>
       </c>
       <c r="C76" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -4056,15 +4359,15 @@
         <v>3</v>
       </c>
       <c r="G76" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H76" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I76" t="s">
-        <v>51</v>
-      </c>
-      <c r="X76">
+        <v>61</v>
+      </c>
+      <c r="AB76">
         <v>5</v>
       </c>
     </row>
@@ -4076,7 +4379,7 @@
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -4088,13 +4391,13 @@
         <v>-40</v>
       </c>
       <c r="G77" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H77" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I77" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78">
@@ -4105,7 +4408,7 @@
         <v>2</v>
       </c>
       <c r="C78" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -4117,33 +4420,39 @@
         <v>-20</v>
       </c>
       <c r="G78" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H78" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I78" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="J78">
         <v>-3</v>
       </c>
       <c r="K78" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L78">
         <v>5</v>
       </c>
-      <c r="R78" t="s">
-        <v>35</v>
-      </c>
-      <c r="S78" t="s">
-        <v>53</v>
-      </c>
-      <c r="U78" t="s">
-        <v>35</v>
-      </c>
-      <c r="X78">
+      <c r="P78" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>40</v>
+      </c>
+      <c r="W78" t="s">
+        <v>41</v>
+      </c>
+      <c r="X78" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB78">
         <v>6</v>
       </c>
     </row>
@@ -4155,7 +4464,7 @@
         <v>2</v>
       </c>
       <c r="C79" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -4167,19 +4476,19 @@
         <v>-17</v>
       </c>
       <c r="G79" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H79" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I79" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J79">
         <v>26</v>
       </c>
       <c r="K79" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L79">
         <v>6</v>
@@ -4190,19 +4499,25 @@
       <c r="O79">
         <v>9</v>
       </c>
-      <c r="R79" t="s">
-        <v>46</v>
-      </c>
-      <c r="S79" t="s">
-        <v>70</v>
-      </c>
-      <c r="U79" t="s">
-        <v>35</v>
-      </c>
-      <c r="W79">
-        <v>6</v>
-      </c>
-      <c r="X79">
+      <c r="P79" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>40</v>
+      </c>
+      <c r="S79">
+        <v>6</v>
+      </c>
+      <c r="W79" t="s">
+        <v>55</v>
+      </c>
+      <c r="X79" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB79">
         <v>6</v>
       </c>
     </row>
@@ -4214,7 +4529,7 @@
         <v>2</v>
       </c>
       <c r="C80" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -4226,10 +4541,10 @@
         <v>-43</v>
       </c>
       <c r="G80" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I80" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -4243,7 +4558,7 @@
         <v>2</v>
       </c>
       <c r="C81" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -4255,19 +4570,19 @@
         <v>-43</v>
       </c>
       <c r="G81" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H81" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I81" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J81">
         <v>13</v>
       </c>
       <c r="K81" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L81">
         <v>5</v>
@@ -4278,19 +4593,25 @@
       <c r="O81">
         <v>5</v>
       </c>
-      <c r="R81" t="s">
-        <v>30</v>
+      <c r="P81" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>70</v>
       </c>
       <c r="S81" t="s">
-        <v>53</v>
-      </c>
-      <c r="U81" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="W81" t="s">
-        <v>76</v>
-      </c>
-      <c r="X81">
+        <v>34</v>
+      </c>
+      <c r="X81" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB81">
         <v>6</v>
       </c>
     </row>
@@ -4302,7 +4623,7 @@
         <v>2</v>
       </c>
       <c r="C82" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -4314,19 +4635,19 @@
         <v>44</v>
       </c>
       <c r="G82" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H82" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I82" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J82">
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L82">
         <v>5</v>
@@ -4337,19 +4658,25 @@
       <c r="O82">
         <v>8</v>
       </c>
-      <c r="R82" t="s">
-        <v>30</v>
+      <c r="P82" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>70</v>
       </c>
       <c r="S82" t="s">
-        <v>53</v>
-      </c>
-      <c r="U82" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="W82" t="s">
-        <v>76</v>
-      </c>
-      <c r="X82">
+        <v>34</v>
+      </c>
+      <c r="X82" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB82">
         <v>6</v>
       </c>
     </row>
@@ -4361,7 +4688,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D83">
         <v>2</v>
@@ -4373,15 +4700,15 @@
         <v>44</v>
       </c>
       <c r="G83" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H83" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="I83" t="s">
-        <v>41</v>
-      </c>
-      <c r="X83">
+        <v>49</v>
+      </c>
+      <c r="AB83">
         <v>6</v>
       </c>
     </row>
@@ -4393,7 +4720,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -4405,36 +4732,39 @@
         <v>-17</v>
       </c>
       <c r="G84" t="s">
+        <v>41</v>
+      </c>
+      <c r="H84" t="s">
         <v>35</v>
       </c>
-      <c r="H84" t="s">
-        <v>31</v>
-      </c>
       <c r="I84" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J84">
         <v>8</v>
       </c>
       <c r="K84" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L84">
         <v>7</v>
       </c>
       <c r="M84" t="s">
-        <v>43</v>
-      </c>
-      <c r="R84" t="s">
-        <v>30</v>
-      </c>
-      <c r="S84" t="s">
-        <v>60</v>
-      </c>
-      <c r="U84" t="s">
-        <v>35</v>
-      </c>
-      <c r="X84">
+        <v>51</v>
+      </c>
+      <c r="P84" t="s">
+        <v>44</v>
+      </c>
+      <c r="W84" t="s">
+        <v>34</v>
+      </c>
+      <c r="X84" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB84">
         <v>5</v>
       </c>
     </row>
@@ -4446,7 +4776,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -4458,36 +4788,39 @@
         <v>-25</v>
       </c>
       <c r="G85" t="s">
+        <v>41</v>
+      </c>
+      <c r="H85" t="s">
         <v>35</v>
       </c>
-      <c r="H85" t="s">
-        <v>31</v>
-      </c>
       <c r="I85" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J85">
         <v>-4</v>
       </c>
       <c r="K85" t="s">
+        <v>37</v>
+      </c>
+      <c r="L85">
+        <v>6</v>
+      </c>
+      <c r="M85" t="s">
         <v>33</v>
       </c>
-      <c r="L85">
-        <v>6</v>
-      </c>
-      <c r="M85" t="s">
-        <v>29</v>
-      </c>
-      <c r="R85" t="s">
-        <v>30</v>
-      </c>
-      <c r="S85" t="s">
-        <v>60</v>
-      </c>
-      <c r="U85" t="s">
-        <v>35</v>
-      </c>
-      <c r="X85">
+      <c r="P85" t="s">
+        <v>44</v>
+      </c>
+      <c r="W85" t="s">
+        <v>34</v>
+      </c>
+      <c r="X85" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB85">
         <v>5</v>
       </c>
     </row>
@@ -4499,7 +4832,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D86">
         <v>3</v>
@@ -4511,19 +4844,19 @@
         <v>-21</v>
       </c>
       <c r="G86" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H86" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I86" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J86">
         <v>14</v>
       </c>
       <c r="K86" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L86">
         <v>7</v>
@@ -4534,16 +4867,19 @@
       <c r="O86">
         <v>6</v>
       </c>
-      <c r="R86" t="s">
-        <v>30</v>
-      </c>
-      <c r="S86" t="s">
-        <v>58</v>
-      </c>
-      <c r="U86" t="s">
-        <v>35</v>
-      </c>
-      <c r="X86">
+      <c r="P86" t="s">
+        <v>66</v>
+      </c>
+      <c r="W86" t="s">
+        <v>34</v>
+      </c>
+      <c r="X86" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB86">
         <v>5</v>
       </c>
     </row>
@@ -4555,7 +4891,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -4567,33 +4903,33 @@
         <v>-35</v>
       </c>
       <c r="G87" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H87" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I87" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="J87">
         <v>-1</v>
       </c>
       <c r="K87" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L87">
         <v>6</v>
       </c>
-      <c r="R87" t="s">
-        <v>46</v>
-      </c>
-      <c r="S87" t="s">
-        <v>47</v>
-      </c>
-      <c r="U87" t="s">
-        <v>35</v>
-      </c>
-      <c r="X87">
+      <c r="W87" t="s">
+        <v>55</v>
+      </c>
+      <c r="X87" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB87">
         <v>5</v>
       </c>
     </row>
@@ -4605,7 +4941,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D88">
         <v>2</v>
@@ -4617,33 +4953,36 @@
         <v>-34</v>
       </c>
       <c r="G88" t="s">
+        <v>41</v>
+      </c>
+      <c r="H88" t="s">
         <v>35</v>
       </c>
-      <c r="H88" t="s">
-        <v>31</v>
-      </c>
       <c r="I88" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J88">
         <v>16</v>
       </c>
       <c r="K88" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L88">
         <v>7</v>
       </c>
       <c r="M88" t="s">
-        <v>43</v>
-      </c>
-      <c r="R88" t="s">
-        <v>35</v>
-      </c>
-      <c r="U88" t="s">
-        <v>30</v>
-      </c>
-      <c r="X88">
+        <v>51</v>
+      </c>
+      <c r="P88" t="s">
+        <v>54</v>
+      </c>
+      <c r="W88" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB88">
         <v>5</v>
       </c>
     </row>
@@ -4655,7 +4994,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -4667,36 +5006,36 @@
         <v>50</v>
       </c>
       <c r="G89" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H89" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I89" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J89">
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L89">
         <v>6</v>
       </c>
       <c r="M89" t="s">
-        <v>43</v>
-      </c>
-      <c r="R89" t="s">
-        <v>46</v>
-      </c>
-      <c r="S89" t="s">
-        <v>47</v>
-      </c>
-      <c r="U89" t="s">
-        <v>30</v>
-      </c>
-      <c r="X89">
+        <v>51</v>
+      </c>
+      <c r="W89" t="s">
+        <v>55</v>
+      </c>
+      <c r="X89" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB89">
         <v>5</v>
       </c>
     </row>
@@ -4708,7 +5047,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D90">
         <v>2</v>
@@ -4720,36 +5059,36 @@
         <v>48</v>
       </c>
       <c r="G90" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H90" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I90" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J90">
         <v>4</v>
       </c>
       <c r="K90" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L90">
         <v>6</v>
       </c>
       <c r="M90" t="s">
-        <v>29</v>
-      </c>
-      <c r="R90" t="s">
-        <v>46</v>
-      </c>
-      <c r="S90" t="s">
-        <v>47</v>
-      </c>
-      <c r="U90" t="s">
-        <v>35</v>
-      </c>
-      <c r="X90">
+        <v>33</v>
+      </c>
+      <c r="W90" t="s">
+        <v>55</v>
+      </c>
+      <c r="X90" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB90">
         <v>5</v>
       </c>
     </row>
@@ -4761,7 +5100,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D91">
         <v>3</v>
@@ -4773,19 +5112,19 @@
         <v>44</v>
       </c>
       <c r="G91" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H91" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I91" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J91">
         <v>10</v>
       </c>
       <c r="K91" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L91">
         <v>6</v>
@@ -4796,16 +5135,19 @@
       <c r="O91">
         <v>1</v>
       </c>
-      <c r="R91" t="s">
-        <v>30</v>
-      </c>
-      <c r="S91" t="s">
-        <v>58</v>
-      </c>
-      <c r="U91" t="s">
-        <v>30</v>
-      </c>
-      <c r="X91">
+      <c r="P91" t="s">
+        <v>66</v>
+      </c>
+      <c r="W91" t="s">
+        <v>34</v>
+      </c>
+      <c r="X91" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB91">
         <v>5</v>
       </c>
     </row>
@@ -4817,7 +5159,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -4829,19 +5171,19 @@
         <v>34</v>
       </c>
       <c r="G92" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H92" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I92" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J92">
         <v>-1</v>
       </c>
       <c r="K92" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L92">
         <v>8</v>
@@ -4852,16 +5194,19 @@
       <c r="O92">
         <v>3</v>
       </c>
-      <c r="R92" t="s">
-        <v>35</v>
-      </c>
-      <c r="S92" t="s">
-        <v>48</v>
-      </c>
-      <c r="U92" t="s">
-        <v>35</v>
-      </c>
-      <c r="X92">
+      <c r="P92" t="s">
+        <v>57</v>
+      </c>
+      <c r="W92" t="s">
+        <v>41</v>
+      </c>
+      <c r="X92" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB92">
         <v>5</v>
       </c>
     </row>
@@ -4873,7 +5218,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D93">
         <v>2</v>
@@ -4885,36 +5230,39 @@
         <v>35</v>
       </c>
       <c r="G93" t="s">
+        <v>41</v>
+      </c>
+      <c r="H93" t="s">
         <v>35</v>
       </c>
-      <c r="H93" t="s">
-        <v>31</v>
-      </c>
       <c r="I93" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J93">
         <v>8</v>
       </c>
       <c r="K93" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L93">
         <v>7</v>
       </c>
       <c r="M93" t="s">
-        <v>37</v>
-      </c>
-      <c r="R93" t="s">
-        <v>30</v>
-      </c>
-      <c r="S93" t="s">
-        <v>60</v>
-      </c>
-      <c r="U93" t="s">
-        <v>35</v>
-      </c>
-      <c r="X93">
+        <v>43</v>
+      </c>
+      <c r="P93" t="s">
+        <v>44</v>
+      </c>
+      <c r="W93" t="s">
+        <v>34</v>
+      </c>
+      <c r="X93" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB93">
         <v>5</v>
       </c>
     </row>
@@ -4926,7 +5274,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D94">
         <v>3</v>
@@ -4938,36 +5286,39 @@
         <v>27</v>
       </c>
       <c r="G94" t="s">
+        <v>41</v>
+      </c>
+      <c r="H94" t="s">
         <v>35</v>
       </c>
-      <c r="H94" t="s">
-        <v>31</v>
-      </c>
       <c r="I94" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J94">
         <v>7</v>
       </c>
       <c r="K94" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L94">
         <v>7</v>
       </c>
       <c r="M94" t="s">
-        <v>43</v>
-      </c>
-      <c r="R94" t="s">
-        <v>30</v>
-      </c>
-      <c r="S94" t="s">
-        <v>60</v>
-      </c>
-      <c r="U94" t="s">
-        <v>35</v>
-      </c>
-      <c r="X94">
+        <v>51</v>
+      </c>
+      <c r="P94" t="s">
+        <v>44</v>
+      </c>
+      <c r="W94" t="s">
+        <v>34</v>
+      </c>
+      <c r="X94" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB94">
         <v>5</v>
       </c>
     </row>
@@ -4979,7 +5330,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -4991,36 +5342,39 @@
         <v>20</v>
       </c>
       <c r="G95" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H95" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I95" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J95">
         <v>11</v>
       </c>
       <c r="K95" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L95">
         <v>6</v>
       </c>
       <c r="M95" t="s">
-        <v>29</v>
-      </c>
-      <c r="R95" t="s">
-        <v>30</v>
-      </c>
-      <c r="S95" t="s">
-        <v>60</v>
-      </c>
-      <c r="U95" t="s">
-        <v>30</v>
-      </c>
-      <c r="X95">
+        <v>33</v>
+      </c>
+      <c r="P95" t="s">
+        <v>44</v>
+      </c>
+      <c r="W95" t="s">
+        <v>34</v>
+      </c>
+      <c r="X95" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB95">
         <v>5</v>
       </c>
     </row>
@@ -5032,7 +5386,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -5044,36 +5398,39 @@
         <v>9</v>
       </c>
       <c r="G96" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H96" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I96" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J96">
         <v>1</v>
       </c>
       <c r="K96" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L96">
         <v>8</v>
       </c>
       <c r="M96" t="s">
-        <v>52</v>
-      </c>
-      <c r="R96" t="s">
-        <v>30</v>
-      </c>
-      <c r="S96" t="s">
-        <v>60</v>
-      </c>
-      <c r="U96" t="s">
-        <v>35</v>
-      </c>
-      <c r="X96">
+        <v>62</v>
+      </c>
+      <c r="P96" t="s">
+        <v>44</v>
+      </c>
+      <c r="W96" t="s">
+        <v>34</v>
+      </c>
+      <c r="X96" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB96">
         <v>5</v>
       </c>
     </row>
@@ -5085,7 +5442,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D97">
         <v>2</v>
@@ -5097,36 +5454,39 @@
         <v>8</v>
       </c>
       <c r="G97" t="s">
+        <v>41</v>
+      </c>
+      <c r="H97" t="s">
         <v>35</v>
       </c>
-      <c r="H97" t="s">
-        <v>31</v>
-      </c>
       <c r="I97" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J97">
         <v>-4</v>
       </c>
       <c r="K97" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L97">
         <v>7</v>
       </c>
       <c r="M97" t="s">
-        <v>34</v>
-      </c>
-      <c r="R97" t="s">
-        <v>30</v>
-      </c>
-      <c r="S97" t="s">
-        <v>63</v>
-      </c>
-      <c r="U97" t="s">
-        <v>30</v>
-      </c>
-      <c r="X97">
+        <v>38</v>
+      </c>
+      <c r="P97" t="s">
+        <v>66</v>
+      </c>
+      <c r="W97" t="s">
+        <v>34</v>
+      </c>
+      <c r="X97" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB97">
         <v>5</v>
       </c>
     </row>
@@ -5138,7 +5498,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D98">
         <v>3</v>
@@ -5150,36 +5510,36 @@
         <v>12</v>
       </c>
       <c r="G98" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H98" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I98" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="J98">
         <v>12</v>
       </c>
       <c r="K98" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L98">
         <v>6</v>
       </c>
       <c r="M98" t="s">
-        <v>37</v>
-      </c>
-      <c r="R98" t="s">
-        <v>46</v>
-      </c>
-      <c r="S98" t="s">
-        <v>47</v>
-      </c>
-      <c r="U98" t="s">
-        <v>30</v>
-      </c>
-      <c r="X98">
+        <v>43</v>
+      </c>
+      <c r="W98" t="s">
+        <v>55</v>
+      </c>
+      <c r="X98" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB98">
         <v>5</v>
       </c>
     </row>
@@ -5191,7 +5551,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -5203,15 +5563,15 @@
         <v>3</v>
       </c>
       <c r="G99" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H99" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I99" t="s">
-        <v>51</v>
-      </c>
-      <c r="X99">
+        <v>61</v>
+      </c>
+      <c r="AB99">
         <v>5</v>
       </c>
     </row>
@@ -5223,7 +5583,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -5235,13 +5595,13 @@
         <v>-40</v>
       </c>
       <c r="G100" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H100" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I100" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="101">
@@ -5252,7 +5612,7 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -5264,39 +5624,42 @@
         <v>-20</v>
       </c>
       <c r="G101" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H101" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I101" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J101">
         <v>10</v>
       </c>
       <c r="K101" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L101">
         <v>6</v>
       </c>
       <c r="M101" t="s">
-        <v>43</v>
-      </c>
-      <c r="R101" t="s">
-        <v>30</v>
-      </c>
-      <c r="S101" t="s">
-        <v>36</v>
-      </c>
-      <c r="U101" t="s">
-        <v>30</v>
-      </c>
-      <c r="W101">
-        <v>3</v>
-      </c>
-      <c r="X101">
+        <v>51</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>40</v>
+      </c>
+      <c r="S101">
+        <v>3</v>
+      </c>
+      <c r="W101" t="s">
+        <v>34</v>
+      </c>
+      <c r="X101" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB101">
         <v>7</v>
       </c>
     </row>
@@ -5308,7 +5671,7 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -5320,36 +5683,42 @@
         <v>-30</v>
       </c>
       <c r="G102" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H102" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I102" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="J102">
         <v>-8</v>
       </c>
       <c r="K102" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L102">
         <v>6</v>
       </c>
-      <c r="R102" t="s">
-        <v>35</v>
-      </c>
-      <c r="S102" t="s">
+      <c r="P102" t="s">
         <v>39</v>
       </c>
-      <c r="U102" t="s">
-        <v>30</v>
-      </c>
-      <c r="W102">
-        <v>3</v>
-      </c>
-      <c r="X102">
+      <c r="Q102" t="s">
+        <v>46</v>
+      </c>
+      <c r="S102">
+        <v>3</v>
+      </c>
+      <c r="W102" t="s">
+        <v>41</v>
+      </c>
+      <c r="X102" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB102">
         <v>7</v>
       </c>
     </row>
@@ -5361,7 +5730,7 @@
         <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -5373,39 +5742,42 @@
         <v>-22</v>
       </c>
       <c r="G103" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H103" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I103" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J103">
         <v>1</v>
       </c>
       <c r="K103" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L103">
         <v>6</v>
       </c>
       <c r="M103" t="s">
-        <v>43</v>
-      </c>
-      <c r="R103" t="s">
-        <v>30</v>
-      </c>
-      <c r="S103" t="s">
-        <v>36</v>
-      </c>
-      <c r="U103" t="s">
-        <v>30</v>
-      </c>
-      <c r="W103">
-        <v>3</v>
-      </c>
-      <c r="X103">
+        <v>51</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>40</v>
+      </c>
+      <c r="S103">
+        <v>3</v>
+      </c>
+      <c r="W103" t="s">
+        <v>34</v>
+      </c>
+      <c r="X103" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB103">
         <v>7</v>
       </c>
     </row>
@@ -5417,7 +5789,7 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D104">
         <v>2</v>
@@ -5429,19 +5801,19 @@
         <v>-23</v>
       </c>
       <c r="G104" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H104" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I104" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J104">
         <v>26</v>
       </c>
       <c r="K104" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L104">
         <v>6</v>
@@ -5452,19 +5824,25 @@
       <c r="O104">
         <v>5</v>
       </c>
-      <c r="R104" t="s">
-        <v>35</v>
-      </c>
-      <c r="S104" t="s">
-        <v>53</v>
-      </c>
-      <c r="U104" t="s">
-        <v>35</v>
-      </c>
-      <c r="W104">
-        <v>6</v>
-      </c>
-      <c r="X104">
+      <c r="P104" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>46</v>
+      </c>
+      <c r="S104">
+        <v>6</v>
+      </c>
+      <c r="W104" t="s">
+        <v>41</v>
+      </c>
+      <c r="X104" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB104">
         <v>7</v>
       </c>
     </row>
@@ -5476,7 +5854,7 @@
         <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -5488,19 +5866,19 @@
         <v>-49</v>
       </c>
       <c r="G105" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H105" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I105" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J105">
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L105">
         <v>6</v>
@@ -5511,19 +5889,25 @@
       <c r="O105">
         <v>6</v>
       </c>
-      <c r="R105" t="s">
-        <v>35</v>
-      </c>
-      <c r="S105" t="s">
-        <v>70</v>
-      </c>
-      <c r="U105" t="s">
-        <v>35</v>
-      </c>
-      <c r="W105">
-        <v>3</v>
-      </c>
-      <c r="X105">
+      <c r="P105" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>40</v>
+      </c>
+      <c r="S105">
+        <v>3</v>
+      </c>
+      <c r="W105" t="s">
+        <v>41</v>
+      </c>
+      <c r="X105" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB105">
         <v>7</v>
       </c>
     </row>
@@ -5535,7 +5919,7 @@
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D106">
         <v>2</v>
@@ -5547,19 +5931,19 @@
         <v>-49</v>
       </c>
       <c r="G106" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H106" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I106" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J106">
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L106">
         <v>6</v>
@@ -5570,19 +5954,25 @@
       <c r="O106">
         <v>2</v>
       </c>
-      <c r="R106" t="s">
-        <v>46</v>
-      </c>
-      <c r="S106" t="s">
-        <v>70</v>
-      </c>
-      <c r="U106" t="s">
-        <v>30</v>
-      </c>
-      <c r="W106">
-        <v>3</v>
-      </c>
-      <c r="X106">
+      <c r="P106" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>40</v>
+      </c>
+      <c r="S106">
+        <v>3</v>
+      </c>
+      <c r="W106" t="s">
+        <v>55</v>
+      </c>
+      <c r="X106" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB106">
         <v>7</v>
       </c>
     </row>
@@ -5594,7 +5984,7 @@
         <v>3</v>
       </c>
       <c r="C107" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D107">
         <v>3</v>
@@ -5606,19 +5996,19 @@
         <v>-49</v>
       </c>
       <c r="G107" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H107" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I107" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J107">
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L107">
         <v>6</v>
@@ -5629,19 +6019,25 @@
       <c r="O107">
         <v>6</v>
       </c>
-      <c r="R107" t="s">
-        <v>35</v>
-      </c>
-      <c r="S107" t="s">
-        <v>53</v>
-      </c>
-      <c r="U107" t="s">
-        <v>30</v>
-      </c>
-      <c r="W107">
-        <v>6</v>
-      </c>
-      <c r="X107">
+      <c r="P107" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>40</v>
+      </c>
+      <c r="S107">
+        <v>6</v>
+      </c>
+      <c r="W107" t="s">
+        <v>41</v>
+      </c>
+      <c r="X107" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB107">
         <v>7</v>
       </c>
     </row>
@@ -5653,7 +6049,7 @@
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D108">
         <v>4</v>
@@ -5665,15 +6061,15 @@
         <v>-49</v>
       </c>
       <c r="G108" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H108" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I108" t="s">
-        <v>78</v>
-      </c>
-      <c r="X108">
+        <v>97</v>
+      </c>
+      <c r="AB108">
         <v>7</v>
       </c>
     </row>
@@ -5685,7 +6081,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -5697,19 +6093,19 @@
         <v>-25</v>
       </c>
       <c r="G109" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H109" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I109" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J109">
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L109">
         <v>7</v>
@@ -5720,16 +6116,16 @@
       <c r="O109">
         <v>3</v>
       </c>
-      <c r="R109" t="s">
-        <v>46</v>
-      </c>
-      <c r="S109" t="s">
-        <v>47</v>
-      </c>
-      <c r="U109" t="s">
-        <v>35</v>
-      </c>
-      <c r="X109">
+      <c r="W109" t="s">
+        <v>55</v>
+      </c>
+      <c r="X109" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB109">
         <v>6</v>
       </c>
     </row>
@@ -5741,7 +6137,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D110">
         <v>2</v>
@@ -5753,36 +6149,39 @@
         <v>-25</v>
       </c>
       <c r="G110" t="s">
+        <v>41</v>
+      </c>
+      <c r="H110" t="s">
         <v>35</v>
       </c>
-      <c r="H110" t="s">
-        <v>31</v>
-      </c>
       <c r="I110" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J110">
         <v>3</v>
       </c>
       <c r="K110" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L110">
         <v>6</v>
       </c>
       <c r="M110" t="s">
-        <v>37</v>
-      </c>
-      <c r="R110" t="s">
-        <v>30</v>
-      </c>
-      <c r="S110" t="s">
-        <v>60</v>
-      </c>
-      <c r="U110" t="s">
-        <v>35</v>
-      </c>
-      <c r="X110">
+        <v>43</v>
+      </c>
+      <c r="P110" t="s">
+        <v>44</v>
+      </c>
+      <c r="W110" t="s">
+        <v>34</v>
+      </c>
+      <c r="X110" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB110">
         <v>6</v>
       </c>
     </row>
@@ -5794,7 +6193,7 @@
         <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D111">
         <v>3</v>
@@ -5806,19 +6205,19 @@
         <v>-28</v>
       </c>
       <c r="G111" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H111" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I111" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J111">
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L111">
         <v>6</v>
@@ -5829,16 +6228,16 @@
       <c r="O111">
         <v>6</v>
       </c>
-      <c r="R111" t="s">
-        <v>46</v>
-      </c>
-      <c r="S111" t="s">
-        <v>47</v>
-      </c>
-      <c r="U111" t="s">
-        <v>35</v>
-      </c>
-      <c r="X111">
+      <c r="W111" t="s">
+        <v>55</v>
+      </c>
+      <c r="X111" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB111">
         <v>6</v>
       </c>
     </row>
@@ -5850,7 +6249,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D112">
         <v>4</v>
@@ -5862,15 +6261,15 @@
         <v>-28</v>
       </c>
       <c r="G112" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H112" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="I112" t="s">
-        <v>41</v>
-      </c>
-      <c r="X112">
+        <v>49</v>
+      </c>
+      <c r="AB112">
         <v>6</v>
       </c>
     </row>
@@ -5882,7 +6281,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -5894,39 +6293,42 @@
         <v>-39</v>
       </c>
       <c r="G113" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H113" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I113" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J113">
         <v>17</v>
       </c>
       <c r="K113" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L113">
         <v>6</v>
       </c>
       <c r="M113" t="s">
-        <v>52</v>
-      </c>
-      <c r="R113" t="s">
-        <v>30</v>
-      </c>
-      <c r="S113" t="s">
-        <v>36</v>
-      </c>
-      <c r="U113" t="s">
-        <v>35</v>
-      </c>
-      <c r="W113">
-        <v>6</v>
-      </c>
-      <c r="X113">
+        <v>62</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>40</v>
+      </c>
+      <c r="S113">
+        <v>6</v>
+      </c>
+      <c r="W113" t="s">
+        <v>34</v>
+      </c>
+      <c r="X113" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB113">
         <v>8</v>
       </c>
     </row>
@@ -5938,7 +6340,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -5950,39 +6352,45 @@
         <v>44</v>
       </c>
       <c r="G114" t="s">
+        <v>41</v>
+      </c>
+      <c r="H114" t="s">
         <v>35</v>
       </c>
-      <c r="H114" t="s">
-        <v>31</v>
-      </c>
       <c r="I114" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J114">
         <v>-20</v>
       </c>
       <c r="K114" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L114">
         <v>6</v>
       </c>
       <c r="M114" t="s">
-        <v>37</v>
-      </c>
-      <c r="R114" t="s">
-        <v>30</v>
-      </c>
-      <c r="S114" t="s">
+        <v>43</v>
+      </c>
+      <c r="P114" t="s">
         <v>39</v>
       </c>
-      <c r="U114" t="s">
-        <v>35</v>
-      </c>
-      <c r="W114">
-        <v>6</v>
-      </c>
-      <c r="X114">
+      <c r="Q114" t="s">
+        <v>40</v>
+      </c>
+      <c r="S114">
+        <v>6</v>
+      </c>
+      <c r="W114" t="s">
+        <v>34</v>
+      </c>
+      <c r="X114" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB114">
         <v>8</v>
       </c>
     </row>
@@ -5994,7 +6402,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D115">
         <v>2</v>
@@ -6006,19 +6414,19 @@
         <v>-36</v>
       </c>
       <c r="G115" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H115" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I115" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J115">
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L115">
         <v>6</v>
@@ -6029,19 +6437,25 @@
       <c r="O115">
         <v>3</v>
       </c>
-      <c r="R115" t="s">
-        <v>35</v>
-      </c>
-      <c r="S115" t="s">
+      <c r="P115" t="s">
         <v>39</v>
       </c>
-      <c r="U115" t="s">
-        <v>35</v>
-      </c>
-      <c r="W115">
-        <v>6</v>
-      </c>
-      <c r="X115">
+      <c r="Q115" t="s">
+        <v>40</v>
+      </c>
+      <c r="S115">
+        <v>6</v>
+      </c>
+      <c r="W115" t="s">
+        <v>41</v>
+      </c>
+      <c r="X115" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB115">
         <v>8</v>
       </c>
     </row>
@@ -6053,7 +6467,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D116">
         <v>3</v>
@@ -6065,19 +6479,19 @@
         <v>-36</v>
       </c>
       <c r="G116" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H116" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I116" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J116">
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L116">
         <v>6</v>
@@ -6088,19 +6502,25 @@
       <c r="O116">
         <v>2</v>
       </c>
-      <c r="R116" t="s">
-        <v>46</v>
-      </c>
-      <c r="S116" t="s">
-        <v>70</v>
-      </c>
-      <c r="U116" t="s">
-        <v>30</v>
-      </c>
-      <c r="W116">
-        <v>3</v>
-      </c>
-      <c r="X116">
+      <c r="P116" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>99</v>
+      </c>
+      <c r="S116">
+        <v>3</v>
+      </c>
+      <c r="W116" t="s">
+        <v>55</v>
+      </c>
+      <c r="X116" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB116">
         <v>8</v>
       </c>
     </row>
@@ -6112,7 +6532,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D117">
         <v>4</v>
@@ -6124,15 +6544,15 @@
         <v>-36</v>
       </c>
       <c r="G117" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H117" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I117" t="s">
-        <v>78</v>
-      </c>
-      <c r="X117">
+        <v>97</v>
+      </c>
+      <c r="AB117">
         <v>8</v>
       </c>
     </row>
@@ -6144,7 +6564,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -6156,33 +6576,33 @@
         <v>-19</v>
       </c>
       <c r="G118" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H118" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I118" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L118">
         <v>6</v>
       </c>
-      <c r="R118" t="s">
-        <v>46</v>
-      </c>
-      <c r="S118" t="s">
-        <v>47</v>
-      </c>
-      <c r="U118" t="s">
-        <v>30</v>
-      </c>
-      <c r="X118">
+      <c r="W118" t="s">
+        <v>55</v>
+      </c>
+      <c r="X118" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB118">
         <v>7</v>
       </c>
     </row>
@@ -6194,7 +6614,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D119">
         <v>2</v>
@@ -6206,36 +6626,39 @@
         <v>-19</v>
       </c>
       <c r="G119" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H119" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I119" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J119">
         <v>5</v>
       </c>
       <c r="K119" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L119">
         <v>7</v>
       </c>
       <c r="M119" t="s">
-        <v>37</v>
-      </c>
-      <c r="R119" t="s">
-        <v>35</v>
-      </c>
-      <c r="S119" t="s">
-        <v>60</v>
-      </c>
-      <c r="U119" t="s">
-        <v>30</v>
-      </c>
-      <c r="X119">
+        <v>43</v>
+      </c>
+      <c r="P119" t="s">
+        <v>44</v>
+      </c>
+      <c r="W119" t="s">
+        <v>41</v>
+      </c>
+      <c r="X119" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB119">
         <v>7</v>
       </c>
     </row>
@@ -6247,7 +6670,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D120">
         <v>3</v>
@@ -6259,36 +6682,39 @@
         <v>-24</v>
       </c>
       <c r="G120" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H120" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I120" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J120">
         <v>6</v>
       </c>
       <c r="K120" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L120">
         <v>6</v>
       </c>
       <c r="M120" t="s">
-        <v>52</v>
-      </c>
-      <c r="R120" t="s">
-        <v>35</v>
-      </c>
-      <c r="S120" t="s">
-        <v>80</v>
-      </c>
-      <c r="U120" t="s">
-        <v>30</v>
-      </c>
-      <c r="X120">
+        <v>62</v>
+      </c>
+      <c r="P120" t="s">
+        <v>66</v>
+      </c>
+      <c r="W120" t="s">
+        <v>41</v>
+      </c>
+      <c r="X120" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB120">
         <v>7</v>
       </c>
     </row>
@@ -6300,7 +6726,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -6312,36 +6738,39 @@
         <v>-30</v>
       </c>
       <c r="G121" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H121" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I121" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J121">
         <v>3</v>
       </c>
       <c r="K121" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L121">
         <v>7</v>
       </c>
       <c r="M121" t="s">
-        <v>37</v>
-      </c>
-      <c r="R121" t="s">
-        <v>35</v>
-      </c>
-      <c r="S121" t="s">
-        <v>80</v>
-      </c>
-      <c r="U121" t="s">
-        <v>30</v>
-      </c>
-      <c r="X121">
+        <v>43</v>
+      </c>
+      <c r="P121" t="s">
+        <v>66</v>
+      </c>
+      <c r="W121" t="s">
+        <v>41</v>
+      </c>
+      <c r="X121" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB121">
         <v>7</v>
       </c>
     </row>
@@ -6353,7 +6782,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -6365,36 +6794,36 @@
         <v>-33</v>
       </c>
       <c r="G122" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H122" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I122" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J122">
         <v>3</v>
       </c>
       <c r="K122" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L122">
         <v>6</v>
       </c>
       <c r="M122" t="s">
-        <v>37</v>
-      </c>
-      <c r="R122" t="s">
-        <v>46</v>
-      </c>
-      <c r="S122" t="s">
-        <v>47</v>
-      </c>
-      <c r="U122" t="s">
-        <v>30</v>
-      </c>
-      <c r="X122">
+        <v>43</v>
+      </c>
+      <c r="W122" t="s">
+        <v>55</v>
+      </c>
+      <c r="X122" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z122" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB122">
         <v>7</v>
       </c>
     </row>
@@ -6406,7 +6835,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D123">
         <v>3</v>
@@ -6418,19 +6847,19 @@
         <v>-36</v>
       </c>
       <c r="G123" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H123" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I123" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J123">
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L123">
         <v>6</v>
@@ -6441,16 +6870,19 @@
       <c r="O123">
         <v>1</v>
       </c>
-      <c r="R123" t="s">
-        <v>46</v>
-      </c>
-      <c r="S123" t="s">
-        <v>70</v>
-      </c>
-      <c r="U123" t="s">
-        <v>30</v>
-      </c>
-      <c r="X123">
+      <c r="P123" t="s">
+        <v>101</v>
+      </c>
+      <c r="W123" t="s">
+        <v>55</v>
+      </c>
+      <c r="X123" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB123">
         <v>7</v>
       </c>
     </row>
@@ -6462,7 +6894,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D124">
         <v>4</v>
@@ -6474,15 +6906,15 @@
         <v>-36</v>
       </c>
       <c r="G124" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H124" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="I124" t="s">
-        <v>64</v>
-      </c>
-      <c r="X124">
+        <v>80</v>
+      </c>
+      <c r="AB124">
         <v>7</v>
       </c>
     </row>
@@ -6494,7 +6926,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -6506,19 +6938,19 @@
         <v>-40</v>
       </c>
       <c r="G125" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H125" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I125" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="J125">
         <v>-15</v>
       </c>
       <c r="K125" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L125">
         <v>6</v>
@@ -6529,19 +6961,25 @@
       <c r="O125">
         <v>9</v>
       </c>
-      <c r="R125" t="s">
-        <v>46</v>
-      </c>
-      <c r="S125" t="s">
-        <v>70</v>
-      </c>
-      <c r="U125" t="s">
-        <v>35</v>
-      </c>
-      <c r="W125">
-        <v>3</v>
-      </c>
-      <c r="X125">
+      <c r="P125" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>40</v>
+      </c>
+      <c r="S125">
+        <v>3</v>
+      </c>
+      <c r="W125" t="s">
+        <v>55</v>
+      </c>
+      <c r="X125" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z125" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB125">
         <v>9</v>
       </c>
     </row>
@@ -6553,7 +6991,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -6565,39 +7003,45 @@
         <v>-25</v>
       </c>
       <c r="G126" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H126" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I126" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J126">
         <v>20</v>
       </c>
       <c r="K126" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L126">
         <v>5</v>
       </c>
       <c r="M126" t="s">
-        <v>37</v>
-      </c>
-      <c r="R126" t="s">
-        <v>35</v>
-      </c>
-      <c r="S126" t="s">
-        <v>53</v>
-      </c>
-      <c r="U126" t="s">
-        <v>30</v>
-      </c>
-      <c r="W126">
-        <v>6</v>
-      </c>
-      <c r="X126">
+        <v>43</v>
+      </c>
+      <c r="P126" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>40</v>
+      </c>
+      <c r="S126">
+        <v>6</v>
+      </c>
+      <c r="W126" t="s">
+        <v>41</v>
+      </c>
+      <c r="X126" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z126" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB126">
         <v>9</v>
       </c>
     </row>
@@ -6609,7 +7053,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D127">
         <v>2</v>
@@ -6621,19 +7065,19 @@
         <v>-45</v>
       </c>
       <c r="G127" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H127" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I127" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J127">
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L127">
         <v>5</v>
@@ -6644,19 +7088,25 @@
       <c r="O127">
         <v>7</v>
       </c>
-      <c r="R127" t="s">
-        <v>30</v>
-      </c>
-      <c r="S127" t="s">
-        <v>53</v>
-      </c>
-      <c r="U127" t="s">
-        <v>30</v>
-      </c>
-      <c r="W127">
-        <v>6</v>
-      </c>
-      <c r="X127">
+      <c r="P127" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>40</v>
+      </c>
+      <c r="S127">
+        <v>6</v>
+      </c>
+      <c r="W127" t="s">
+        <v>34</v>
+      </c>
+      <c r="X127" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z127" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB127">
         <v>9</v>
       </c>
     </row>
@@ -6668,7 +7118,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D128">
         <v>3</v>
@@ -6680,19 +7130,19 @@
         <v>-45</v>
       </c>
       <c r="G128" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H128" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="I128" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J128">
         <v>0</v>
       </c>
       <c r="K128" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L128">
         <v>6</v>
@@ -6703,19 +7153,25 @@
       <c r="O128">
         <v>3</v>
       </c>
-      <c r="R128" t="s">
-        <v>46</v>
-      </c>
-      <c r="S128" t="s">
-        <v>70</v>
-      </c>
-      <c r="U128" t="s">
-        <v>35</v>
-      </c>
-      <c r="W128">
-        <v>6</v>
-      </c>
-      <c r="X128">
+      <c r="P128" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>40</v>
+      </c>
+      <c r="S128">
+        <v>6</v>
+      </c>
+      <c r="W128" t="s">
+        <v>55</v>
+      </c>
+      <c r="X128" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z128" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB128">
         <v>9</v>
       </c>
     </row>
@@ -6727,7 +7183,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D129">
         <v>4</v>
@@ -6739,39 +7195,45 @@
         <v>-45</v>
       </c>
       <c r="G129" t="s">
+        <v>41</v>
+      </c>
+      <c r="H129" t="s">
         <v>35</v>
       </c>
-      <c r="H129" t="s">
-        <v>31</v>
-      </c>
       <c r="I129" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J129">
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L129">
         <v>6</v>
       </c>
       <c r="M129" t="s">
-        <v>43</v>
-      </c>
-      <c r="R129" t="s">
-        <v>46</v>
-      </c>
-      <c r="S129" t="s">
-        <v>70</v>
-      </c>
-      <c r="U129" t="s">
-        <v>30</v>
-      </c>
-      <c r="W129">
-        <v>3</v>
-      </c>
-      <c r="X129">
+        <v>51</v>
+      </c>
+      <c r="P129" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>40</v>
+      </c>
+      <c r="S129">
+        <v>3</v>
+      </c>
+      <c r="W129" t="s">
+        <v>55</v>
+      </c>
+      <c r="X129" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z129" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB129">
         <v>9</v>
       </c>
     </row>
